--- a/bank_management_system.xlsx
+++ b/bank_management_system.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\testing\testing projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" firstSheet="5" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="16" r:id="rId1"/>
@@ -2885,9 +2885,6 @@
     <t xml:space="preserve">project name </t>
   </si>
   <si>
-    <t>GPTL bank</t>
-  </si>
-  <si>
     <t>v1.0</t>
   </si>
   <si>
@@ -3045,6 +3042,9 @@
   </si>
   <si>
     <t>CS</t>
+  </si>
+  <si>
+    <t>GTPL bank</t>
   </si>
 </sst>
 </file>
@@ -3283,803 +3283,7 @@
   </cellStyles>
   <dxfs count="122">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5A6BD"/>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF9CB9C"/>
-          <bgColor rgb="FFF9CB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF61658E"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -4304,46 +3508,826 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Droid Sans"/>
-        <scheme val="none"/>
+        <color theme="0"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF61658E"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="0"/>
-        <name val="Droid Sans"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF6B26B"/>
+          <fgColor indexed="64"/>
           <bgColor rgb="FF272E64"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5A6BD"/>
+          <bgColor rgb="FFD5A6BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9CB9C"/>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4477,30 +4461,46 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Droid Sans"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
+        <name val="Droid Sans"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor rgb="FFF6B26B"/>
           <bgColor rgb="FF272E64"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5661,7 +5661,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="F4:J6" totalsRowShown="0" headerRowDxfId="113" dataDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="F4:J6" totalsRowShown="0" headerRowDxfId="121" dataDxfId="120">
   <autoFilter ref="F4:J6">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5670,32 +5670,32 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" name="project name " dataDxfId="118"/>
-    <tableColumn id="2" name="Version #" dataDxfId="117"/>
-    <tableColumn id="3" name="By" dataDxfId="116"/>
-    <tableColumn id="4" name="Date" dataDxfId="115"/>
-    <tableColumn id="5" name="Description" dataDxfId="114"/>
+    <tableColumn id="1" name="project name " dataDxfId="119"/>
+    <tableColumn id="2" name="Version #" dataDxfId="118"/>
+    <tableColumn id="3" name="By" dataDxfId="117"/>
+    <tableColumn id="4" name="Date" dataDxfId="116"/>
+    <tableColumn id="5" name="Description" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:M25" headerRowDxfId="121" dataDxfId="98" totalsRowDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:M25" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
   <tableColumns count="13">
-    <tableColumn id="1" name="Bug Title" totalsRowLabel="Total" dataDxfId="111"/>
-    <tableColumn id="2" name="Description" dataDxfId="110"/>
-    <tableColumn id="3" name="Steps To Reproduce" dataDxfId="109"/>
-    <tableColumn id="4" name="Expected Result" dataDxfId="108"/>
-    <tableColumn id="5" name="Actual Result" dataDxfId="107"/>
-    <tableColumn id="6" name="Environment" dataDxfId="106"/>
-    <tableColumn id="7" name="Screenshot/Attachement" dataDxfId="105"/>
-    <tableColumn id="10" name="Severity" dataDxfId="104"/>
-    <tableColumn id="11" name="Priority" dataDxfId="103"/>
-    <tableColumn id="8" name="Reported By" dataDxfId="102"/>
-    <tableColumn id="9" name="Date" dataDxfId="101"/>
-    <tableColumn id="12" name="Status" dataDxfId="100"/>
-    <tableColumn id="13" name="module" dataDxfId="99" totalsRowDxfId="119"/>
+    <tableColumn id="1" name="Bug Title" totalsRowLabel="Total" dataDxfId="13"/>
+    <tableColumn id="2" name="Description" dataDxfId="12"/>
+    <tableColumn id="3" name="Steps To Reproduce" dataDxfId="11"/>
+    <tableColumn id="4" name="Expected Result" dataDxfId="10"/>
+    <tableColumn id="5" name="Actual Result" dataDxfId="9"/>
+    <tableColumn id="6" name="Environment" dataDxfId="8"/>
+    <tableColumn id="7" name="Screenshot/Attachement" dataDxfId="7"/>
+    <tableColumn id="10" name="Severity" dataDxfId="6"/>
+    <tableColumn id="11" name="Priority" dataDxfId="5"/>
+    <tableColumn id="8" name="Reported By" dataDxfId="4"/>
+    <tableColumn id="9" name="Date" dataDxfId="3"/>
+    <tableColumn id="12" name="Status" dataDxfId="2"/>
+    <tableColumn id="13" name="module" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="1" showLastColumn="1" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="5" spans="6:10" ht="48.9" customHeight="1">
       <c r="F5" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="G5" s="25" t="s">
         <v>416</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>417</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>414</v>
@@ -6169,19 +6169,19 @@
         <v>273</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>241</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>283</v>
@@ -6367,22 +6367,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I9:I16">
-    <cfRule type="cellIs" dxfId="25" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="17" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I16">
-    <cfRule type="cellIs" dxfId="24" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I16">
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="19" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I16">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="20" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6397,22 +6397,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="9" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6427,22 +6427,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6457,7 +6457,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="BLOCKED">
+    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="BLOCKED">
       <formula>NOT(ISERROR(SEARCH("BLOCKED",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6546,7 +6546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="61.5">
+    <row r="3" spans="1:9" ht="49.2">
       <c r="A3" s="1" t="s">
         <v>294</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>300</v>
@@ -6757,7 +6757,7 @@
         <v>301</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>300</v>
@@ -6846,22 +6846,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I5:I16">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I16">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I16">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I16">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6876,22 +6876,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7165,22 +7165,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7302,7 +7302,7 @@
         <v>352</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="78.599999999999994" customHeight="1">
@@ -7329,7 +7329,7 @@
         <v>357</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>0</v>
@@ -7341,12 +7341,12 @@
         <v>352</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="73.5" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>371</v>
@@ -7368,7 +7368,7 @@
         <v>364</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>0</v>
@@ -7380,7 +7380,7 @@
         <v>352</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="69" customHeight="1">
@@ -7407,7 +7407,7 @@
         <v>357</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>352</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="86.4">
@@ -7446,7 +7446,7 @@
         <v>364</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>0</v>
@@ -7458,7 +7458,7 @@
         <v>352</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="86.4">
@@ -7485,7 +7485,7 @@
         <v>357</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>352</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="172.8">
@@ -7524,7 +7524,7 @@
         <v>364</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>0</v>
@@ -7536,7 +7536,7 @@
         <v>352</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="144">
@@ -7575,7 +7575,7 @@
         <v>352</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="144">
@@ -7614,7 +7614,7 @@
         <v>352</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="158.4">
@@ -7653,7 +7653,7 @@
         <v>352</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="158.4">
@@ -7692,7 +7692,7 @@
         <v>352</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="158.4">
@@ -7731,7 +7731,7 @@
         <v>352</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="158.4">
@@ -7770,7 +7770,7 @@
         <v>352</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="90.9" customHeight="1">
@@ -7797,7 +7797,7 @@
         <v>357</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>0</v>
@@ -7809,7 +7809,7 @@
         <v>352</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="86.4">
@@ -7820,7 +7820,7 @@
         <v>408</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>409</v>
@@ -7848,18 +7848,18 @@
         <v>352</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="86.4">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="72">
       <c r="A17" s="20" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>137</v>
@@ -7875,7 +7875,7 @@
         <v>357</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J17" s="13" t="s">
         <v>0</v>
@@ -7887,18 +7887,18 @@
         <v>352</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="86.4">
       <c r="A18" s="20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>423</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>424</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>409</v>
@@ -7926,18 +7926,18 @@
         <v>352</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="86.4">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="72">
       <c r="A19" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>431</v>
-      </c>
       <c r="C19" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>137</v>
@@ -7953,7 +7953,7 @@
         <v>357</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>0</v>
@@ -7965,18 +7965,18 @@
         <v>352</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="86.4">
       <c r="A20" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>433</v>
-      </c>
       <c r="C20" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>409</v>
@@ -8004,18 +8004,18 @@
         <v>352</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="86.4">
       <c r="A21" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>137</v>
@@ -8031,7 +8031,7 @@
         <v>357</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>0</v>
@@ -8043,18 +8043,18 @@
         <v>352</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="201.6">
       <c r="A22" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>316</v>
@@ -8082,18 +8082,18 @@
         <v>352</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="172.8">
       <c r="A23" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>325</v>
@@ -8121,18 +8121,18 @@
         <v>352</v>
       </c>
       <c r="M23" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="201.6">
       <c r="A24" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>445</v>
-      </c>
       <c r="C24" s="18" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>325</v>
@@ -8160,18 +8160,18 @@
         <v>352</v>
       </c>
       <c r="M24" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="201.6">
       <c r="A25" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>448</v>
-      </c>
       <c r="C25" s="18" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>325</v>
@@ -8199,7 +8199,7 @@
         <v>352</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -8346,22 +8346,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="97" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="96" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="94" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8635,22 +8635,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I8">
-    <cfRule type="cellIs" dxfId="93" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8">
-    <cfRule type="cellIs" dxfId="92" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8">
-    <cfRule type="cellIs" dxfId="91" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8">
-    <cfRule type="cellIs" dxfId="90" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9183,22 +9183,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="89" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="6" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="88" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="7" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="87" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="8" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="86" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="9" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9213,22 +9213,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I17">
-    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I17">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I17">
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I17">
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="5" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9475,22 +9475,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I5">
-    <cfRule type="cellIs" dxfId="81" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="22" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I5">
-    <cfRule type="cellIs" dxfId="80" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="23" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I5">
-    <cfRule type="cellIs" dxfId="79" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="24" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I5">
-    <cfRule type="cellIs" dxfId="78" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="25" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9505,42 +9505,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="77" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="17" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="76" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="18" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="75" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="19" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="74" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="20" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="73" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="6" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="72" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="71" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="8" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="70" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9555,22 +9555,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="69" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="68" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="67" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="66" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9844,22 +9844,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="65" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="22" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="64" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="23" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="63" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="24" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="62" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="25" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9874,22 +9874,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="61" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="17" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="60" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="18" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="59" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="19" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="58" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="20" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9904,42 +9904,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I6">
-    <cfRule type="cellIs" dxfId="57" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="12" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I6">
-    <cfRule type="cellIs" dxfId="56" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="13" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I6">
-    <cfRule type="cellIs" dxfId="55" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="14" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I6">
-    <cfRule type="cellIs" dxfId="54" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="15" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="53" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="7" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="52" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="8" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="51" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="9" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="50" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9954,22 +9954,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="5" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10356,42 +10356,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I8 I12">
-    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="11" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8 I12">
-    <cfRule type="cellIs" dxfId="44" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="12" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8 I12">
-    <cfRule type="cellIs" dxfId="43" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="13" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I8 I12">
-    <cfRule type="cellIs" dxfId="42" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="14" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10675,42 +10675,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="37" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="36" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="35" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I8">
-    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="9" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I4">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10887,10 +10887,10 @@
         <v>268</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>241</v>
@@ -11082,22 +11082,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I16">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="4" operator="equal">
       <formula>"N/E"</formula>
     </cfRule>
   </conditionalFormatting>
